--- a/output/laminas_comunales/comunal_s_isapre_a_2021_la_araucania.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2021_la_araucania.xlsx
@@ -384,367 +384,367 @@
         </is>
       </c>
       <c r="C2">
-        <v>48416</v>
+        <v>16.60538879438073</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Pucón</t>
         </is>
       </c>
       <c r="C3">
-        <v>5437</v>
+        <v>8.924176725653346</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Angol</t>
+          <t>Villarrica</t>
         </is>
       </c>
       <c r="C4">
-        <v>4474</v>
+        <v>7.992884759566617</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Padre Las Casas</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="C5">
-        <v>3513</v>
+        <v>7.920546684134122</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C6">
-        <v>3046</v>
+        <v>6.201969602094837</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Vilcún</t>
         </is>
       </c>
       <c r="C7">
-        <v>2179</v>
+        <v>4.627638123403683</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lautaro</t>
+          <t>Padre Las Casas</t>
         </is>
       </c>
       <c r="C8">
-        <v>1893</v>
+        <v>4.606790196309847</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vilcún</t>
+          <t>Pitrufquén</t>
         </is>
       </c>
       <c r="C9">
-        <v>1377</v>
+        <v>4.58965530288698</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>Lautaro</t>
         </is>
       </c>
       <c r="C10">
-        <v>1213</v>
+        <v>4.565296032798746</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>Curacautín</t>
         </is>
       </c>
       <c r="C11">
-        <v>992</v>
+        <v>4.538969616908851</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Collipulli</t>
+          <t>Traiguén</t>
         </is>
       </c>
       <c r="C12">
-        <v>965</v>
+        <v>4.240800646987465</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Curacautín</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C13">
-        <v>859</v>
+        <v>3.946388682055101</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="C14">
-        <v>842</v>
+        <v>3.670178374472293</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Purén</t>
         </is>
       </c>
       <c r="C15">
-        <v>839</v>
+        <v>3.591073393053591</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Freire</t>
+          <t>Toltén</t>
         </is>
       </c>
       <c r="C16">
-        <v>712</v>
+        <v>3.478600742622631</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Loncoche</t>
         </is>
       </c>
       <c r="C17">
-        <v>629</v>
+        <v>3.473454065426344</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Gorbea</t>
         </is>
       </c>
       <c r="C18">
-        <v>562</v>
+        <v>3.376913474804546</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gorbea</t>
+          <t>Melipeuco</t>
         </is>
       </c>
       <c r="C19">
-        <v>514</v>
+        <v>3.20326150262085</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Purén</t>
+          <t>Lonquimay</t>
         </is>
       </c>
       <c r="C20">
-        <v>457</v>
+        <v>2.973020944266951</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Renaico</t>
+          <t>Nueva Imperial</t>
         </is>
       </c>
       <c r="C21">
-        <v>424</v>
+        <v>2.90781181298549</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Cunco</t>
         </is>
       </c>
       <c r="C22">
-        <v>356</v>
+        <v>2.898401237751418</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Freire</t>
         </is>
       </c>
       <c r="C23">
-        <v>335</v>
+        <v>2.852907000040069</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Teodoro Schmidt</t>
+          <t>Perquenco</t>
         </is>
       </c>
       <c r="C24">
-        <v>280</v>
+        <v>2.841141920502664</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cholchol</t>
+          <t>Los Sauces</t>
         </is>
       </c>
       <c r="C25">
-        <v>272</v>
+        <v>2.658849195527679</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Carahue</t>
         </is>
       </c>
       <c r="C26">
-        <v>232</v>
+        <v>2.469765980838699</v>
       </c>
     </row>
     <row r="27">
@@ -759,82 +759,82 @@
         </is>
       </c>
       <c r="C27">
-        <v>227</v>
+        <v>2.457241827235332</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Melipeuco</t>
+          <t>Cholchol</t>
         </is>
       </c>
       <c r="C28">
-        <v>220</v>
+        <v>2.237026071222962</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Perquenco</t>
+          <t>Curarrehue</t>
         </is>
       </c>
       <c r="C29">
-        <v>208</v>
+        <v>2.228312678741659</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Teodoro Schmidt</t>
         </is>
       </c>
       <c r="C30">
-        <v>207</v>
+        <v>1.811125485122898</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Los Sauces</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="C31">
-        <v>195</v>
+        <v>1.755580779417329</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Curarrehue</t>
+          <t>Galvarino</t>
         </is>
       </c>
       <c r="C32">
-        <v>187</v>
+        <v>1.645992366412214</v>
       </c>
     </row>
     <row r="33">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="C33">
-        <v>135</v>
+        <v>1.506864605424713</v>
       </c>
     </row>
   </sheetData>
@@ -905,7 +905,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
